--- a/Result/profitability/6152.xlsx
+++ b/Result/profitability/6152.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2525</v>
+        <v>-0.17</v>
       </c>
       <c r="N2" t="n">
-        <v>15.9225</v>
+        <v>17.44625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.17625</v>
+        <v>-0.10375</v>
       </c>
       <c r="N3" t="n">
-        <v>16.115</v>
+        <v>18.18375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08750000000000002</v>
+        <v>-0.007500000000000021</v>
       </c>
       <c r="N4" t="n">
-        <v>16.95375</v>
+        <v>18.75375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01625</v>
+        <v>0.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>17.32125</v>
+        <v>19.38375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23375</v>
+        <v>0.31875</v>
       </c>
       <c r="N6" t="n">
-        <v>17.8525</v>
+        <v>20.065</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2837499999999999</v>
+        <v>0.37625</v>
       </c>
       <c r="N7" t="n">
-        <v>18.25875</v>
+        <v>20.69625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3825</v>
+        <v>0.47125</v>
       </c>
       <c r="N8" t="n">
-        <v>19.1275</v>
+        <v>20.36125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6152</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>625</v>
+      </c>
+      <c r="D75" t="n">
+        <v>435</v>
+      </c>
+      <c r="E75" t="n">
+        <v>190</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>83</v>
+      </c>
+      <c r="K75" t="n">
+        <v>82</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.01125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.227272727272727</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.48193359375</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.556818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.191335740072202</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
